--- a/08_tables/q7_twfe_descriptive_statistics.xlsx
+++ b/08_tables/q7_twfe_descriptive_statistics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,63 +473,63 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>twfe_LS</t>
+          <t>twfe_WR</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>700</v>
       </c>
       <c r="C2" t="n">
-        <v>8.130639019197718e-15</v>
+        <v>-4.872293045212116e-16</v>
       </c>
       <c r="D2" t="n">
-        <v>2.573395479892854</v>
+        <v>16.76557648172726</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.439571428571405</v>
+        <v>-33.77516004557859</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.380499999999982</v>
+        <v>-7.740661649694442</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08285714285714718</v>
+        <v>1.339171921876385</v>
       </c>
       <c r="H2" t="n">
-        <v>1.38507142857144</v>
+        <v>6.680275184226836</v>
       </c>
       <c r="I2" t="n">
-        <v>19.20814285714287</v>
+        <v>117.0120387449064</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>twfe_WR</t>
+          <t>twfe_LS</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>700</v>
       </c>
       <c r="C3" t="n">
-        <v>1.218073261303029e-16</v>
+        <v>8.130639019197718e-15</v>
       </c>
       <c r="D3" t="n">
-        <v>16.76557648172725</v>
+        <v>2.573395479892853</v>
       </c>
       <c r="E3" t="n">
-        <v>-33.77516004557859</v>
+        <v>-9.439571428571405</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.740661649694447</v>
+        <v>-1.380499999999982</v>
       </c>
       <c r="G3" t="n">
-        <v>1.339171921876385</v>
+        <v>0.08285714285714718</v>
       </c>
       <c r="H3" t="n">
-        <v>6.680275184226836</v>
+        <v>1.38507142857144</v>
       </c>
       <c r="I3" t="n">
-        <v>117.0120387449064</v>
+        <v>19.20814285714287</v>
       </c>
     </row>
     <row r="4">
@@ -542,10 +542,10 @@
         <v>700</v>
       </c>
       <c r="C4" t="n">
-        <v>9.135549459772716e-16</v>
+        <v>9.389314722544181e-16</v>
       </c>
       <c r="D4" t="n">
-        <v>1.943272811215971</v>
+        <v>1.943272811215969</v>
       </c>
       <c r="E4" t="n">
         <v>-6.586255063450912</v>

--- a/08_tables/q7_twfe_descriptive_statistics.xlsx
+++ b/08_tables/q7_twfe_descriptive_statistics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/q7_twfe_descriptive_statistics.xlsx
+++ b/08_tables/q7_twfe_descriptive_statistics.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,49 +417,49 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>twfe_WR</t>
         </is>
@@ -502,7 +490,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>twfe_LS</t>
         </is>
@@ -533,7 +521,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>twfe_i</t>
         </is>
